--- a/config/yunying/playpassport_recharge.xlsx
+++ b/config/yunying/playpassport_recharge.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="27945" windowHeight="12375" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="playpassport_recharge" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="playpassport_recharge" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1125,19 +1125,11 @@
         </is>
       </c>
       <c r="B2" s="1" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
           <t>""</t>
@@ -1237,21 +1229,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr"/>
       <c r="B4" s="1" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1261,7 +1239,7 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>豪華パス</t>
+          <t>豪华通行证</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1299,12 +1277,6 @@
           <t>198</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1314,7 +1286,7 @@
       </c>
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t>豪華パス</t>
+          <t>豪华通行证</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1352,12 +1324,6 @@
           <t>788</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1367,7 +1333,7 @@
       </c>
       <c r="B7" s="1" t="inlineStr">
         <is>
-          <t>豪華パス</t>
+          <t>豪华通行证</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1405,12 +1371,6 @@
           <t>788</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1420,7 +1380,7 @@
       </c>
       <c r="B8" s="1" t="inlineStr">
         <is>
-          <t>豪華パス</t>
+          <t>豪华通行证</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1458,12 +1418,6 @@
           <t>788</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1473,7 +1427,7 @@
       </c>
       <c r="B9" s="1" t="inlineStr">
         <is>
-          <t>豪華パス</t>
+          <t>豪华通行证</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1511,12 +1465,6 @@
           <t>788</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1526,7 +1474,7 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>豪華パス</t>
+          <t>豪华通行证</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1564,12 +1512,6 @@
           <t>588</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
